--- a/RFQ Generator Beta Version/Templates/MA TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/MA TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\bin\Debug\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0B7D7B-59ED-4C5E-A513-A90D5F1F2C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0179798A-A479-4BCE-AEAD-AFDCC2FF34C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{46D794FF-3BF6-4A02-A5D7-C081D03B9DC5}"/>
   </bookViews>
@@ -159,9 +159,6 @@
     <t>PO cancellation fee is applied after receipt order</t>
   </si>
   <si>
-    <t>Prices quoted are in Ringgit Malaysia (RM)</t>
-  </si>
-  <si>
     <t>rfq_code</t>
   </si>
   <si>
@@ -189,13 +186,16 @@
     <t>_validity</t>
   </si>
   <si>
-    <t>delivery_time</t>
-  </si>
-  <si>
     <t>delivery_term</t>
   </si>
   <si>
     <t>client_name</t>
+  </si>
+  <si>
+    <t>header_delivery_time</t>
+  </si>
+  <si>
+    <t>Prices quoted are in (RM)</t>
   </si>
 </sst>
 </file>
@@ -520,32 +520,32 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1082,23 +1082,23 @@
       <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:19" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
       <c r="C7" s="5"/>
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:19" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="I8" s="46" t="s">
+      <c r="I8" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="J8" s="46"/>
+      <c r="J8" s="45"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1109,7 +1109,7 @@
         <v>30</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J9" s="18"/>
       <c r="S9" s="2"/>
@@ -1126,7 +1126,7 @@
         <v>29</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J10" s="18"/>
       <c r="Q10" s="6"/>
@@ -1145,7 +1145,7 @@
         <v>31</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J11" s="18"/>
       <c r="Q11" s="6"/>
@@ -1175,18 +1175,18 @@
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
-      <c r="H13" s="47" t="s">
+      <c r="H13" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="48"/>
-      <c r="J13" s="49"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
       <c r="S13" s="2"/>
     </row>
     <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
       <c r="J14" s="2"/>
       <c r="S14" s="2"/>
     </row>
@@ -1213,14 +1213,14 @@
       <c r="B17" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="26" t="s">
         <v>26</v>
       </c>
@@ -1240,21 +1240,21 @@
     <row r="18" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="30" t="s">
         <v>46</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="30" t="s">
-        <v>47</v>
       </c>
       <c r="J19" s="30" t="s">
         <v>32</v>
@@ -1263,12 +1263,12 @@
     <row r="20" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="31"/>
       <c r="B20" s="31"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
       <c r="I20" s="29"/>
       <c r="J20" s="32"/>
       <c r="S20" s="33"/>
@@ -1280,11 +1280,11 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
       <c r="J21" s="40" t="s">
         <v>35</v>
       </c>
@@ -1297,11 +1297,11 @@
       <c r="D22" s="34"/>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
-      <c r="G22" s="42" t="s">
+      <c r="G22" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
       <c r="J22" s="40" t="s">
         <v>36</v>
       </c>
@@ -1309,13 +1309,13 @@
     </row>
     <row r="23" spans="1:19" s="14" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="15"/>
-      <c r="G23" s="42" t="s">
+      <c r="G23" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
       <c r="J23" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
@@ -1372,7 +1372,7 @@
         <v>37</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -1390,7 +1390,7 @@
         <v>37</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
@@ -1408,7 +1408,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -1426,7 +1426,7 @@
         <v>37</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>

--- a/RFQ Generator Beta Version/Templates/MA TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/MA TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0179798A-A479-4BCE-AEAD-AFDCC2FF34C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1990B964-40C3-433A-8D63-9404382F22A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{46D794FF-3BF6-4A02-A5D7-C081D03B9DC5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="PRICED" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$J$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$J$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$1:$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>Term and Condition</t>
   </si>
@@ -66,9 +66,6 @@
     <t>COMMERCIAL</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL </t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Price  </t>
   </si>
   <si>
@@ -141,15 +138,9 @@
     <t>SUB TOTAL</t>
   </si>
   <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
     <t>sub_total</t>
   </si>
   <si>
-    <t>_discount</t>
-  </si>
-  <si>
     <t>:</t>
   </si>
   <si>
@@ -178,9 +169,6 @@
   </si>
   <si>
     <t>unit_price</t>
-  </si>
-  <si>
-    <t>summary_total_price</t>
   </si>
   <si>
     <t>_validity</t>
@@ -426,7 +414,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -514,38 +502,35 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -646,13 +631,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>594360</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1006,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C861DB86-F116-4FC5-A99F-F10CF8E1A1D4}">
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1" customWidth="1"/>
@@ -1082,23 +1067,23 @@
       <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:19" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="5"/>
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:19" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="I8" s="45" t="s">
+      <c r="I8" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="J8" s="45"/>
+      <c r="J8" s="42"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1106,10 +1091,10 @@
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J9" s="18"/>
       <c r="S9" s="2"/>
@@ -1123,10 +1108,10 @@
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J10" s="18"/>
       <c r="Q10" s="6"/>
@@ -1142,10 +1127,10 @@
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
       <c r="H11" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J11" s="18"/>
       <c r="Q11" s="6"/>
@@ -1175,18 +1160,18 @@
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="45"/>
       <c r="S13" s="2"/>
     </row>
     <row r="14" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
       <c r="J14" s="2"/>
       <c r="S14" s="2"/>
     </row>
@@ -1208,24 +1193,24 @@
     </row>
     <row r="17" spans="1:19" s="28" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="26" t="s">
         <v>24</v>
-      </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="26" t="s">
-        <v>25</v>
       </c>
       <c r="K17" s="27"/>
       <c r="L17" s="27"/>
@@ -1240,35 +1225,35 @@
     <row r="18" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="30" t="s">
-        <v>46</v>
-      </c>
       <c r="J19" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="31"/>
       <c r="B20" s="31"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
       <c r="I20" s="29"/>
       <c r="J20" s="32"/>
       <c r="S20" s="33"/>
@@ -1280,70 +1265,72 @@
       <c r="D21" s="34"/>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
-      <c r="G21" s="41" t="s">
+      <c r="G21" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="40" t="s">
-        <v>35</v>
-      </c>
       <c r="S21" s="33"/>
     </row>
-    <row r="22" spans="1:19" s="14" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="41" t="s">
+    <row r="22" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="D22" s="15"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="36"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="S22" s="33"/>
-    </row>
-    <row r="23" spans="1:19" s="14" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="15"/>
-      <c r="G23" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="39" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="D24" s="15"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="30"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="36"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+      <c r="D26" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
@@ -1352,10 +1339,16 @@
       <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
+      <c r="A27" s="14" t="s">
+        <v>10</v>
+      </c>
       <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="C27" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
@@ -1365,14 +1358,14 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="14"/>
@@ -1383,14 +1376,14 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E29" s="14"/>
       <c r="F29" s="14"/>
@@ -1401,14 +1394,14 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -1419,14 +1412,14 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
@@ -1436,16 +1429,10 @@
       <c r="J31" s="17"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>14</v>
-      </c>
+      <c r="A32" s="14"/>
       <c r="B32" s="14"/>
-      <c r="C32" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
       <c r="G32" s="14"/>
@@ -1454,37 +1441,39 @@
       <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
       <c r="J33" s="17"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
+      <c r="A34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
       <c r="J34" s="17"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
+      <c r="A35" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -1515,7 +1504,7 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
@@ -1530,9 +1519,7 @@
       <c r="V37" s="4"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
-        <v>19</v>
-      </c>
+      <c r="A38" s="17"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -1546,9 +1533,7 @@
       <c r="V38" s="4"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A39" s="17" t="s">
-        <v>20</v>
-      </c>
+      <c r="A39" s="17"/>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -1562,7 +1547,9 @@
       <c r="V39" s="4"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A40" s="17"/>
+      <c r="A40" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -1575,66 +1562,34 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
+    <row r="41" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
+    <row r="42" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="1.2">
+      <c r="A42" s="37" t="s">
+        <v>21</v>
+      </c>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
     </row>
-    <row r="43" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>20</v>
+      </c>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
     </row>
-    <row r="44" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A44" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A45" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="G23:I23"/>
+  <mergeCells count="8">
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="G21:I21"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C17:H17"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G21:I21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.55118110236220474" right="0.23622047244094491" top="0.47244094488188981" bottom="0.62992125984251968" header="0.31496062992125984" footer="0.31496062992125984"/>
